--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2021_los_rios.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2021_los_rios.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:27</t>
+    <t xml:space="preserve">2026-09-24 01:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -739,7 +739,7 @@
         <v>0.2</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>-0.2</v>
@@ -759,10 +759,10 @@
         <v>11</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>-0.66</v>
@@ -785,10 +785,10 @@
         <v>0.16</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="13">
@@ -799,16 +799,16 @@
         <v>19</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>11</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>0.48</v>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2021_los_rios.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2021_los_rios.xlsx
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:17</t>
+    <t xml:space="preserve">2026-10-01 23:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2021_los_rios.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2021_los_rios.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:15</t>
+    <t xml:space="preserve">2026-10-05 19:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
